--- a/#HongKong_anonymized.xlsx
+++ b/#HongKong_anonymized.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20492,7 +20492,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21921,7 +21921,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23164,7 +23164,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23627,7 +23627,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24273,7 +24273,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26315,7 +26315,7 @@
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27704,7 +27704,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27743,7 +27743,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28399,7 +28399,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31099,7 +31099,7 @@
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31642,7 +31642,7 @@
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="J957" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33787,7 +33787,7 @@
       </c>
       <c r="J978" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -34255,7 +34255,7 @@
       </c>
       <c r="J992" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
